--- a/schoolDocs/StudentImportData/Class5_ImportReady.xlsx
+++ b/schoolDocs/StudentImportData/Class5_ImportReady.xlsx
@@ -778,27 +778,27 @@
   <dimension ref="A1:U26"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="23.423" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="18.71" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="10.426" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="11.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="25.708" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="17.567" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="15.139" bestFit="true" customWidth="true" style="0"/>
-    <col min="10" max="10" width="24.565" bestFit="true" customWidth="true" style="0"/>
-    <col min="11" max="11" width="29.279" bestFit="true" customWidth="true" style="0"/>
-    <col min="12" max="12" width="35.277" bestFit="true" customWidth="true" style="0"/>
-    <col min="13" max="13" width="16.425" bestFit="true" customWidth="true" style="0"/>
-    <col min="14" max="14" width="26.993" bestFit="true" customWidth="true" style="0"/>
-    <col min="15" max="15" width="16.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="16" max="16" width="38.848" bestFit="true" customWidth="true" style="0"/>
-    <col min="17" max="17" width="16.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="18" max="18" width="23.423" bestFit="true" customWidth="true" style="0"/>
-    <col min="19" max="19" width="15.139" bestFit="true" customWidth="true" style="0"/>
-    <col min="20" max="20" width="22.28" bestFit="true" customWidth="true" style="0"/>
-    <col min="21" max="21" width="126.112" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="9.283" customWidth="true" style="0"/>
+    <col min="2" max="2" width="23.423" customWidth="true" style="0"/>
+    <col min="3" max="3" width="18.71" customWidth="true" style="0"/>
+    <col min="4" max="4" width="10.426" customWidth="true" style="0"/>
+    <col min="5" max="5" width="9.283" customWidth="true" style="0"/>
+    <col min="6" max="6" width="11.569" customWidth="true" style="0"/>
+    <col min="7" max="7" width="25.708" customWidth="true" style="0"/>
+    <col min="8" max="8" width="17.567" customWidth="true" style="0"/>
+    <col min="9" max="9" width="15.139" customWidth="true" style="0"/>
+    <col min="10" max="10" width="24.565" customWidth="true" style="0"/>
+    <col min="11" max="11" width="29.279" customWidth="true" style="0"/>
+    <col min="12" max="12" width="35.277" customWidth="true" style="0"/>
+    <col min="13" max="13" width="16.425" customWidth="true" style="0"/>
+    <col min="14" max="14" width="26.993" customWidth="true" style="0"/>
+    <col min="15" max="15" width="16.282" customWidth="true" style="0"/>
+    <col min="16" max="16" width="38.848" customWidth="true" style="0"/>
+    <col min="17" max="17" width="16.282" customWidth="true" style="0"/>
+    <col min="18" max="18" width="23.423" customWidth="true" style="0"/>
+    <col min="19" max="19" width="15.139" customWidth="true" style="0"/>
+    <col min="20" max="20" width="22.28" customWidth="true" style="0"/>
+    <col min="21" max="21" width="126.112" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" customHeight="1" ht="30">
@@ -888,6 +888,8 @@
       <c r="H2" t="s">
         <v>25</v>
       </c>
+      <c r="I2"/>
+      <c r="J2"/>
       <c r="K2">
         <v>16200</v>
       </c>
@@ -926,6 +928,11 @@
       <c r="H3" t="s">
         <v>32</v>
       </c>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3">
+        <v>0</v>
+      </c>
       <c r="L3" t="s">
         <v>33</v>
       </c>
@@ -961,8 +968,10 @@
       <c r="H4" t="s">
         <v>25</v>
       </c>
+      <c r="I4"/>
+      <c r="J4"/>
       <c r="K4" s="5">
-        <v>10000</v>
+        <v>16200</v>
       </c>
       <c r="L4" t="s">
         <v>38</v>
@@ -1005,6 +1014,11 @@
       <c r="H5" t="s">
         <v>32</v>
       </c>
+      <c r="I5"/>
+      <c r="J5"/>
+      <c r="K5">
+        <v>0</v>
+      </c>
       <c r="L5" t="s">
         <v>44</v>
       </c>
@@ -1049,6 +1063,7 @@
       <c r="I6">
         <v>25</v>
       </c>
+      <c r="J6"/>
       <c r="K6">
         <v>12150</v>
       </c>
@@ -1093,6 +1108,11 @@
       <c r="H7" t="s">
         <v>32</v>
       </c>
+      <c r="I7"/>
+      <c r="J7"/>
+      <c r="K7">
+        <v>0</v>
+      </c>
       <c r="L7" t="s">
         <v>55</v>
       </c>
@@ -1131,6 +1151,8 @@
       <c r="H8" t="s">
         <v>59</v>
       </c>
+      <c r="I8"/>
+      <c r="J8"/>
       <c r="K8">
         <v>16200</v>
       </c>
@@ -1172,8 +1194,9 @@
       <c r="I9">
         <v>25</v>
       </c>
+      <c r="J9"/>
       <c r="K9">
-        <v>12200</v>
+        <v>12150</v>
       </c>
       <c r="L9" t="s">
         <v>63</v>
@@ -1213,6 +1236,8 @@
       <c r="H10" t="s">
         <v>59</v>
       </c>
+      <c r="I10"/>
+      <c r="J10"/>
       <c r="K10">
         <v>16200</v>
       </c>
@@ -1248,6 +1273,8 @@
       <c r="H11" t="s">
         <v>59</v>
       </c>
+      <c r="I11"/>
+      <c r="J11"/>
       <c r="K11">
         <v>16200</v>
       </c>
@@ -1286,6 +1313,11 @@
       <c r="H12" t="s">
         <v>32</v>
       </c>
+      <c r="I12"/>
+      <c r="J12"/>
+      <c r="K12">
+        <v>0</v>
+      </c>
       <c r="L12" t="s">
         <v>72</v>
       </c>
@@ -1327,6 +1359,11 @@
       <c r="H13" t="s">
         <v>32</v>
       </c>
+      <c r="I13"/>
+      <c r="J13"/>
+      <c r="K13">
+        <v>0</v>
+      </c>
       <c r="L13" t="s">
         <v>75</v>
       </c>
@@ -1368,11 +1405,12 @@
       <c r="H14" t="s">
         <v>48</v>
       </c>
+      <c r="I14"/>
       <c r="J14">
         <v>15000</v>
       </c>
       <c r="K14">
-        <v>15000</v>
+        <v>15000.0</v>
       </c>
       <c r="L14" t="s">
         <v>79</v>
@@ -1412,6 +1450,8 @@
       <c r="H15" t="s">
         <v>59</v>
       </c>
+      <c r="I15"/>
+      <c r="J15"/>
       <c r="K15">
         <v>16200</v>
       </c>
@@ -1447,6 +1487,11 @@
       <c r="H16" t="s">
         <v>32</v>
       </c>
+      <c r="I16"/>
+      <c r="J16"/>
+      <c r="K16">
+        <v>0</v>
+      </c>
       <c r="L16" t="s">
         <v>84</v>
       </c>
@@ -1488,8 +1533,10 @@
       <c r="H17" t="s">
         <v>25</v>
       </c>
+      <c r="I17"/>
+      <c r="J17"/>
       <c r="K17">
-        <v>10000</v>
+        <v>3500</v>
       </c>
       <c r="L17" t="s">
         <v>38</v>
@@ -1532,8 +1579,9 @@
       <c r="I18">
         <v>25</v>
       </c>
+      <c r="J18"/>
       <c r="K18" s="5">
-        <v>3000</v>
+        <v>9150</v>
       </c>
       <c r="L18" t="s">
         <v>94</v>
@@ -1576,8 +1624,10 @@
       <c r="H19" t="s">
         <v>25</v>
       </c>
+      <c r="I19"/>
+      <c r="J19"/>
       <c r="K19">
-        <v>10000</v>
+        <v>12200</v>
       </c>
       <c r="L19" t="s">
         <v>98</v>
@@ -1617,8 +1667,10 @@
       <c r="H20" t="s">
         <v>25</v>
       </c>
+      <c r="I20"/>
+      <c r="J20"/>
       <c r="K20">
-        <v>3000</v>
+        <v>12200</v>
       </c>
       <c r="L20" t="s">
         <v>102</v>
@@ -1658,6 +1710,11 @@
       <c r="H21" t="s">
         <v>32</v>
       </c>
+      <c r="I21"/>
+      <c r="J21"/>
+      <c r="K21">
+        <v>0</v>
+      </c>
       <c r="L21" t="s">
         <v>106</v>
       </c>
@@ -1702,6 +1759,7 @@
       <c r="I22">
         <v>25</v>
       </c>
+      <c r="J22"/>
       <c r="K22">
         <v>9150</v>
       </c>
@@ -1746,11 +1804,12 @@
       <c r="H23" t="s">
         <v>48</v>
       </c>
+      <c r="I23"/>
       <c r="J23">
         <v>11200</v>
       </c>
       <c r="K23">
-        <v>11200</v>
+        <v>11200.0</v>
       </c>
       <c r="L23" t="s">
         <v>26</v>
@@ -1793,11 +1852,12 @@
       <c r="H24" t="s">
         <v>48</v>
       </c>
+      <c r="I24"/>
       <c r="J24">
         <v>11000</v>
       </c>
       <c r="K24">
-        <v>11000</v>
+        <v>11000.0</v>
       </c>
       <c r="L24" t="s">
         <v>114</v>
@@ -1836,6 +1896,11 @@
       </c>
       <c r="H25" t="s">
         <v>32</v>
+      </c>
+      <c r="I25"/>
+      <c r="J25"/>
+      <c r="K25">
+        <v>0</v>
       </c>
       <c r="L25" t="s">
         <v>117</v>
@@ -1877,6 +1942,11 @@
       </c>
       <c r="H26" t="s">
         <v>32</v>
+      </c>
+      <c r="I26"/>
+      <c r="J26"/>
+      <c r="K26">
+        <v>0</v>
       </c>
       <c r="L26" t="s">
         <v>120</v>

--- a/schoolDocs/StudentImportData/Class5_ImportReady.xlsx
+++ b/schoolDocs/StudentImportData/Class5_ImportReady.xlsx
@@ -14,8 +14,34 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="U1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <rFont val="Calibri"/>
+            <b val="false"/>
+            <i val="false"/>
+            <strike val="false"/>
+            <color rgb="FF000000"/>
+            <sz val="11"/>
+            <u val="none"/>
+          </rPr>
+          <t xml:space="preserve">Only for RTE students. Alphanumeric, e.g. 26MS011157 (Year+StateCode+Sequence). Leave blank for non-RTE.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="119">
   <si>
     <t>Sr No</t>
   </si>
@@ -77,7 +103,7 @@
     <t>DGA Admission No</t>
   </si>
   <si>
-    <t>Notes for Verification (ignored on import)</t>
+    <t>RTE Application No</t>
   </si>
   <si>
     <t>Ayush Gaikwad</t>
@@ -125,7 +151,7 @@
     <t>19km</t>
   </si>
   <si>
-    <t>RTE — fees paid by government</t>
+    <t>25MS000030</t>
   </si>
   <si>
     <t>Swarup Sodnwar</t>
@@ -143,9 +169,6 @@
     <t>Owns shoes shop</t>
   </si>
   <si>
-    <t>Partial — ₹10000 of ₹16200 collected</t>
-  </si>
-  <si>
     <t>Smitaj Chavan</t>
   </si>
   <si>
@@ -158,6 +181,9 @@
     <t>Asha worker</t>
   </si>
   <si>
+    <t>25MS000031</t>
+  </si>
+  <si>
     <t>Mit Patel</t>
   </si>
   <si>
@@ -176,9 +202,6 @@
     <t>Hardware shop</t>
   </si>
   <si>
-    <t>Discount 25% on boys fee ₹16200 = ₹12150 payable — full paid</t>
-  </si>
-  <si>
     <t>Yash Gardade</t>
   </si>
   <si>
@@ -191,6 +214,9 @@
     <t>Parlour</t>
   </si>
   <si>
+    <t>25MS000032</t>
+  </si>
+  <si>
     <t>Aryan Devkule</t>
   </si>
   <si>
@@ -200,9 +226,6 @@
     <t>08/12/2018</t>
   </si>
   <si>
-    <t>CoC student — full ₹16200 collected</t>
-  </si>
-  <si>
     <t>Abhimanyu Dudhal</t>
   </si>
   <si>
@@ -215,9 +238,6 @@
     <t>Milk shop and transport business</t>
   </si>
   <si>
-    <t>DGA total ₹12200 but 25% of ₹16200 = ₹12150 — ₹50 difference. System will calculate ₹12150. Please verify.</t>
-  </si>
-  <si>
     <t>Vansh Badhe</t>
   </si>
   <si>
@@ -239,6 +259,9 @@
     <t>Worker</t>
   </si>
   <si>
+    <t>25MS000033</t>
+  </si>
+  <si>
     <t>Asad Pathan</t>
   </si>
   <si>
@@ -251,15 +274,15 @@
     <t>11km</t>
   </si>
   <si>
+    <t>25MS000034</t>
+  </si>
+  <si>
     <t>Saksham Hondavajkar</t>
   </si>
   <si>
     <t>01/02/2019</t>
   </si>
   <si>
-    <t>No standard fee category — ₹15000 used as custom fee. Please verify.</t>
-  </si>
-  <si>
     <t>Mohit Jinwal</t>
   </si>
   <si>
@@ -281,6 +304,9 @@
     <t>Brick Worker</t>
   </si>
   <si>
+    <t>25MS000035</t>
+  </si>
+  <si>
     <t>Swara Shelar</t>
   </si>
   <si>
@@ -293,9 +319,6 @@
     <t>Service</t>
   </si>
   <si>
-    <t>Partial — ₹10000 of ₹12200 collected</t>
-  </si>
-  <si>
     <t>Samruddhi Dudhal</t>
   </si>
   <si>
@@ -305,9 +328,6 @@
     <t>Tea Shop</t>
   </si>
   <si>
-    <t>DGA total ₹9150 but G col blank — assumed 25% discount. Collected ₹3000 partial. Please verify.</t>
-  </si>
-  <si>
     <t>Tanishka Chavan</t>
   </si>
   <si>
@@ -329,15 +349,15 @@
     <t>Shop</t>
   </si>
   <si>
-    <t>Partial — ₹3000 of ₹12200 collected</t>
-  </si>
-  <si>
     <t>Sarveksha Gaikwad</t>
   </si>
   <si>
     <t>08/02/2019</t>
   </si>
   <si>
+    <t>25MS000036</t>
+  </si>
+  <si>
     <t>Shubra Tele</t>
   </si>
   <si>
@@ -347,24 +367,15 @@
     <t>Veterinary Doctor</t>
   </si>
   <si>
-    <t>DGA total ₹9150 but G col blank — assumed 25% discount. Full amount paid. Please verify.</t>
-  </si>
-  <si>
     <t>Renuka Khandekar</t>
   </si>
   <si>
-    <t>No standard fee category — ₹11200 used as custom fee. Please verify.</t>
-  </si>
-  <si>
     <t>Shruti Jagtap</t>
   </si>
   <si>
     <t>24/01/2019</t>
   </si>
   <si>
-    <t>No standard fee category — ₹11000 used as custom fee. Please verify.</t>
-  </si>
-  <si>
     <t>Jyoti Jadhav</t>
   </si>
   <si>
@@ -374,6 +385,9 @@
     <t>Driver</t>
   </si>
   <si>
+    <t>25MS000037</t>
+  </si>
+  <si>
     <t>Tanishka Bhosale</t>
   </si>
   <si>
@@ -381,6 +395,9 @@
   </si>
   <si>
     <t>Door seller</t>
+  </si>
+  <si>
+    <t>25MS000038</t>
   </si>
 </sst>
 </file>
@@ -432,12 +449,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF7B3F00"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFF3CD"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
@@ -445,6 +456,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD5EAD0"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E4057"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -466,16 +483,16 @@
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="2" numFmtId="0" fillId="4" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="5" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="3" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="5" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="4" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -798,7 +815,7 @@
     <col min="18" max="18" width="23.423" customWidth="true" style="0"/>
     <col min="19" max="19" width="15.139" customWidth="true" style="0"/>
     <col min="20" max="20" width="22.28" customWidth="true" style="0"/>
-    <col min="21" max="21" width="126.112" customWidth="true" style="0"/>
+    <col min="21" max="21" width="20" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" customHeight="1" ht="30">
@@ -832,10 +849,10 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
@@ -862,7 +879,7 @@
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="5" t="s">
         <v>20</v>
       </c>
     </row>
@@ -908,6 +925,7 @@
       <c r="R2" t="s">
         <v>30</v>
       </c>
+      <c r="U2"/>
     </row>
     <row r="3" spans="1:21">
       <c r="A3">
@@ -970,7 +988,7 @@
       </c>
       <c r="I4"/>
       <c r="J4"/>
-      <c r="K4" s="5">
+      <c r="K4" s="4">
         <v>16200</v>
       </c>
       <c r="L4" t="s">
@@ -988,16 +1006,14 @@
       <c r="R4" t="s">
         <v>41</v>
       </c>
-      <c r="U4" t="s">
-        <v>42</v>
-      </c>
+      <c r="U4"/>
     </row>
     <row r="5" spans="1:21">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
         <v>22</v>
@@ -1020,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M5" t="s">
         <v>39</v>
@@ -1029,13 +1045,13 @@
         <v>28</v>
       </c>
       <c r="P5" t="s">
+        <v>44</v>
+      </c>
+      <c r="R5" t="s">
         <v>45</v>
       </c>
-      <c r="R5" t="s">
+      <c r="U5" t="s">
         <v>46</v>
-      </c>
-      <c r="U5" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:21">
@@ -1082,16 +1098,14 @@
       <c r="R6" t="s">
         <v>30</v>
       </c>
-      <c r="U6" t="s">
-        <v>53</v>
-      </c>
+      <c r="U6"/>
     </row>
     <row r="7" spans="1:21">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D7" t="s">
         <v>22</v>
@@ -1114,7 +1128,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M7" t="s">
         <v>50</v>
@@ -1123,13 +1137,13 @@
         <v>51</v>
       </c>
       <c r="P7" t="s">
+        <v>55</v>
+      </c>
+      <c r="R7" t="s">
         <v>56</v>
       </c>
-      <c r="R7" t="s">
+      <c r="U7" t="s">
         <v>57</v>
-      </c>
-      <c r="U7" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:21">
@@ -1165,16 +1179,14 @@
       <c r="N8" t="s">
         <v>35</v>
       </c>
-      <c r="U8" t="s">
-        <v>61</v>
-      </c>
+      <c r="U8"/>
     </row>
     <row r="9" spans="1:21">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D9" t="s">
         <v>22</v>
@@ -1199,30 +1211,28 @@
         <v>12150</v>
       </c>
       <c r="L9" t="s">
+        <v>62</v>
+      </c>
+      <c r="M9" t="s">
         <v>63</v>
-      </c>
-      <c r="M9" t="s">
-        <v>64</v>
       </c>
       <c r="N9" t="s">
         <v>28</v>
       </c>
       <c r="P9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R9" t="s">
         <v>30</v>
       </c>
-      <c r="U9" s="5" t="s">
-        <v>66</v>
-      </c>
+      <c r="U9" s="4"/>
     </row>
     <row r="10" spans="1:21">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D10" t="s">
         <v>22</v>
@@ -1242,7 +1252,7 @@
         <v>16200</v>
       </c>
       <c r="L10" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="M10" t="s">
         <v>34</v>
@@ -1250,16 +1260,14 @@
       <c r="N10" t="s">
         <v>35</v>
       </c>
-      <c r="U10" t="s">
-        <v>61</v>
-      </c>
+      <c r="U10"/>
     </row>
     <row r="11" spans="1:21">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D11" t="s">
         <v>22</v>
@@ -1279,7 +1287,7 @@
         <v>16200</v>
       </c>
       <c r="L11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="M11" t="s">
         <v>34</v>
@@ -1287,16 +1295,14 @@
       <c r="N11" t="s">
         <v>35</v>
       </c>
-      <c r="U11" t="s">
-        <v>61</v>
-      </c>
+      <c r="U11"/>
     </row>
     <row r="12" spans="1:21">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D12" t="s">
         <v>22</v>
@@ -1319,7 +1325,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M12" t="s">
         <v>50</v>
@@ -1328,13 +1334,13 @@
         <v>51</v>
       </c>
       <c r="P12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="R12" t="s">
         <v>30</v>
       </c>
       <c r="U12" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:21">
@@ -1342,7 +1348,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="s">
         <v>22</v>
@@ -1365,22 +1371,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="s">
+        <v>74</v>
+      </c>
+      <c r="M13" t="s">
         <v>75</v>
       </c>
-      <c r="M13" t="s">
+      <c r="N13" t="s">
         <v>76</v>
       </c>
-      <c r="N13" t="s">
+      <c r="P13" t="s">
+        <v>71</v>
+      </c>
+      <c r="R13" t="s">
+        <v>71</v>
+      </c>
+      <c r="U13" t="s">
         <v>77</v>
-      </c>
-      <c r="P13" t="s">
-        <v>73</v>
-      </c>
-      <c r="R13" t="s">
-        <v>73</v>
-      </c>
-      <c r="U13" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:21">
@@ -1422,21 +1428,19 @@
         <v>28</v>
       </c>
       <c r="P14" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="R14" t="s">
         <v>30</v>
       </c>
-      <c r="U14" t="s">
-        <v>80</v>
-      </c>
+      <c r="U14"/>
     </row>
     <row r="15" spans="1:21">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D15" t="s">
         <v>22</v>
@@ -1456,7 +1460,7 @@
         <v>16200</v>
       </c>
       <c r="L15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M15" t="s">
         <v>34</v>
@@ -1464,16 +1468,14 @@
       <c r="N15" t="s">
         <v>35</v>
       </c>
-      <c r="U15" t="s">
-        <v>61</v>
-      </c>
+      <c r="U15"/>
     </row>
     <row r="16" spans="1:21">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D16" t="s">
         <v>22</v>
@@ -1493,22 +1495,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="s">
+        <v>83</v>
+      </c>
+      <c r="M16" t="s">
         <v>84</v>
       </c>
-      <c r="M16" t="s">
+      <c r="N16" t="s">
         <v>85</v>
       </c>
-      <c r="N16" t="s">
+      <c r="P16" t="s">
         <v>86</v>
-      </c>
-      <c r="P16" t="s">
-        <v>87</v>
       </c>
       <c r="R16" t="s">
         <v>30</v>
       </c>
       <c r="U16" t="s">
-        <v>36</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:21">
@@ -1553,16 +1555,14 @@
       <c r="R17" t="s">
         <v>91</v>
       </c>
-      <c r="U17" t="s">
-        <v>92</v>
-      </c>
+      <c r="U17"/>
     </row>
     <row r="18" spans="1:21">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D18" t="s">
         <v>89</v>
@@ -1580,34 +1580,32 @@
         <v>25</v>
       </c>
       <c r="J18"/>
-      <c r="K18" s="5">
+      <c r="K18" s="4">
         <v>9150</v>
       </c>
       <c r="L18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M18" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N18" t="s">
         <v>28</v>
       </c>
       <c r="P18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="R18" t="s">
         <v>30</v>
       </c>
-      <c r="U18" s="5" t="s">
-        <v>96</v>
-      </c>
+      <c r="U18" s="4"/>
     </row>
     <row r="19" spans="1:21">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D19" t="s">
         <v>89</v>
@@ -1630,27 +1628,25 @@
         <v>12200</v>
       </c>
       <c r="L19" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="M19" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="N19" t="s">
         <v>28</v>
       </c>
       <c r="R19" t="s">
-        <v>100</v>
-      </c>
-      <c r="U19" t="s">
-        <v>92</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="U19"/>
     </row>
     <row r="20" spans="1:21">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D20" t="s">
         <v>89</v>
@@ -1673,7 +1669,7 @@
         <v>12200</v>
       </c>
       <c r="L20" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="M20" t="s">
         <v>50</v>
@@ -1682,21 +1678,19 @@
         <v>51</v>
       </c>
       <c r="P20" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R20" t="s">
         <v>30</v>
       </c>
-      <c r="U20" t="s">
-        <v>104</v>
-      </c>
+      <c r="U20"/>
     </row>
     <row r="21" spans="1:21">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D21" t="s">
         <v>89</v>
@@ -1716,7 +1710,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M21" t="s">
         <v>39</v>
@@ -1725,13 +1719,13 @@
         <v>28</v>
       </c>
       <c r="P21" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R21" t="s">
         <v>30</v>
       </c>
       <c r="U21" t="s">
-        <v>36</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -1739,7 +1733,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D22" t="s">
         <v>89</v>
@@ -1764,7 +1758,7 @@
         <v>9150</v>
       </c>
       <c r="L22" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="M22" t="s">
         <v>50</v>
@@ -1773,21 +1767,19 @@
         <v>51</v>
       </c>
       <c r="P22" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="R22" t="s">
         <v>30</v>
       </c>
-      <c r="U22" s="5" t="s">
-        <v>110</v>
-      </c>
+      <c r="U22" s="4"/>
     </row>
     <row r="23" spans="1:21">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D23" t="s">
         <v>89</v>
@@ -1821,21 +1813,19 @@
         <v>28</v>
       </c>
       <c r="P23" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="R23" t="s">
         <v>30</v>
       </c>
-      <c r="U23" s="5" t="s">
-        <v>112</v>
-      </c>
+      <c r="U23" s="4"/>
     </row>
     <row r="24" spans="1:21">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D24" t="s">
         <v>89</v>
@@ -1860,7 +1850,7 @@
         <v>11000.0</v>
       </c>
       <c r="L24" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="M24" t="s">
         <v>27</v>
@@ -1869,21 +1859,19 @@
         <v>28</v>
       </c>
       <c r="P24" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="R24" t="s">
         <v>30</v>
       </c>
-      <c r="U24" s="5" t="s">
-        <v>115</v>
-      </c>
+      <c r="U24" s="4"/>
     </row>
     <row r="25" spans="1:21">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D25" t="s">
         <v>89</v>
@@ -1903,7 +1891,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="M25" t="s">
         <v>50</v>
@@ -1912,13 +1900,13 @@
         <v>51</v>
       </c>
       <c r="P25" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="R25" t="s">
         <v>30</v>
       </c>
       <c r="U25" t="s">
-        <v>36</v>
+        <v>114</v>
       </c>
     </row>
     <row r="26" spans="1:21">
@@ -1926,7 +1914,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D26" t="s">
         <v>89</v>
@@ -1949,7 +1937,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="M26" t="s">
         <v>39</v>
@@ -1958,13 +1946,13 @@
         <v>28</v>
       </c>
       <c r="P26" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="R26" t="s">
         <v>30</v>
       </c>
       <c r="U26" t="s">
-        <v>36</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -1979,6 +1967,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <legacyDrawing r:id="rId_comments_vml1"/>
   <tableParts count="0"/>
 </worksheet>
 </file>
--- a/schoolDocs/StudentImportData/Class5_ImportReady.xlsx
+++ b/schoolDocs/StudentImportData/Class5_ImportReady.xlsx
@@ -925,6 +925,9 @@
       <c r="R2" t="s">
         <v>30</v>
       </c>
+      <c r="S2">
+        <v>27000010088</v>
+      </c>
       <c r="U2"/>
     </row>
     <row r="3" spans="1:21">
@@ -960,6 +963,9 @@
       <c r="N3" t="s">
         <v>35</v>
       </c>
+      <c r="S3">
+        <v>27000010089</v>
+      </c>
       <c r="U3" t="s">
         <v>36</v>
       </c>
@@ -1006,6 +1012,9 @@
       <c r="R4" t="s">
         <v>41</v>
       </c>
+      <c r="S4">
+        <v>27000010090</v>
+      </c>
       <c r="U4"/>
     </row>
     <row r="5" spans="1:21">
@@ -1050,6 +1059,9 @@
       <c r="R5" t="s">
         <v>45</v>
       </c>
+      <c r="S5">
+        <v>27000010091</v>
+      </c>
       <c r="U5" t="s">
         <v>46</v>
       </c>
@@ -1097,6 +1109,9 @@
       </c>
       <c r="R6" t="s">
         <v>30</v>
+      </c>
+      <c r="S6">
+        <v>27000010092</v>
       </c>
       <c r="U6"/>
     </row>
@@ -1142,6 +1157,9 @@
       <c r="R7" t="s">
         <v>56</v>
       </c>
+      <c r="S7">
+        <v>27000010093</v>
+      </c>
       <c r="U7" t="s">
         <v>57</v>
       </c>
@@ -1179,6 +1197,9 @@
       <c r="N8" t="s">
         <v>35</v>
       </c>
+      <c r="S8">
+        <v>27000010094</v>
+      </c>
       <c r="U8"/>
     </row>
     <row r="9" spans="1:21">
@@ -1224,6 +1245,9 @@
       </c>
       <c r="R9" t="s">
         <v>30</v>
+      </c>
+      <c r="S9">
+        <v>27000010095</v>
       </c>
       <c r="U9" s="4"/>
     </row>
@@ -1260,6 +1284,9 @@
       <c r="N10" t="s">
         <v>35</v>
       </c>
+      <c r="S10">
+        <v>27000010096</v>
+      </c>
       <c r="U10"/>
     </row>
     <row r="11" spans="1:21">
@@ -1295,6 +1322,9 @@
       <c r="N11" t="s">
         <v>35</v>
       </c>
+      <c r="S11">
+        <v>27000010097</v>
+      </c>
       <c r="U11"/>
     </row>
     <row r="12" spans="1:21">
@@ -1339,6 +1369,9 @@
       <c r="R12" t="s">
         <v>30</v>
       </c>
+      <c r="S12">
+        <v>27000010098</v>
+      </c>
       <c r="U12" t="s">
         <v>72</v>
       </c>
@@ -1385,6 +1418,9 @@
       <c r="R13" t="s">
         <v>71</v>
       </c>
+      <c r="S13">
+        <v>27000010099</v>
+      </c>
       <c r="U13" t="s">
         <v>77</v>
       </c>
@@ -1432,6 +1468,9 @@
       </c>
       <c r="R14" t="s">
         <v>30</v>
+      </c>
+      <c r="S14">
+        <v>27000010100</v>
       </c>
       <c r="U14"/>
     </row>
@@ -1468,6 +1507,9 @@
       <c r="N15" t="s">
         <v>35</v>
       </c>
+      <c r="S15">
+        <v>27000010101</v>
+      </c>
       <c r="U15"/>
     </row>
     <row r="16" spans="1:21">
@@ -1509,6 +1551,9 @@
       <c r="R16" t="s">
         <v>30</v>
       </c>
+      <c r="S16">
+        <v>27000010102</v>
+      </c>
       <c r="U16" t="s">
         <v>87</v>
       </c>
@@ -1555,6 +1600,9 @@
       <c r="R17" t="s">
         <v>91</v>
       </c>
+      <c r="S17">
+        <v>27000010103</v>
+      </c>
       <c r="U17"/>
     </row>
     <row r="18" spans="1:21">
@@ -1597,6 +1645,9 @@
       </c>
       <c r="R18" t="s">
         <v>30</v>
+      </c>
+      <c r="S18">
+        <v>27000010104</v>
       </c>
       <c r="U18" s="4"/>
     </row>
@@ -1639,6 +1690,9 @@
       <c r="R19" t="s">
         <v>98</v>
       </c>
+      <c r="S19">
+        <v>27000010105</v>
+      </c>
       <c r="U19"/>
     </row>
     <row r="20" spans="1:21">
@@ -1683,6 +1737,9 @@
       <c r="R20" t="s">
         <v>30</v>
       </c>
+      <c r="S20">
+        <v>27000010106</v>
+      </c>
       <c r="U20"/>
     </row>
     <row r="21" spans="1:21">
@@ -1724,6 +1781,9 @@
       <c r="R21" t="s">
         <v>30</v>
       </c>
+      <c r="S21">
+        <v>27000010107</v>
+      </c>
       <c r="U21" t="s">
         <v>104</v>
       </c>
@@ -1772,6 +1832,9 @@
       <c r="R22" t="s">
         <v>30</v>
       </c>
+      <c r="S22">
+        <v>27000010108</v>
+      </c>
       <c r="U22" s="4"/>
     </row>
     <row r="23" spans="1:21">
@@ -1818,6 +1881,9 @@
       <c r="R23" t="s">
         <v>30</v>
       </c>
+      <c r="S23">
+        <v>27000010109</v>
+      </c>
       <c r="U23" s="4"/>
     </row>
     <row r="24" spans="1:21">
@@ -1863,6 +1929,9 @@
       </c>
       <c r="R24" t="s">
         <v>30</v>
+      </c>
+      <c r="S24">
+        <v>27000010110</v>
       </c>
       <c r="U24" s="4"/>
     </row>
@@ -1905,6 +1974,9 @@
       <c r="R25" t="s">
         <v>30</v>
       </c>
+      <c r="S25">
+        <v>27000010111</v>
+      </c>
       <c r="U25" t="s">
         <v>114</v>
       </c>
@@ -1950,6 +2022,9 @@
       </c>
       <c r="R26" t="s">
         <v>30</v>
+      </c>
+      <c r="S26">
+        <v>27000010112</v>
       </c>
       <c r="U26" t="s">
         <v>118</v>
